--- a/Documents and results/SS/SS_validering_v19.5.xlsx
+++ b/Documents and results/SS/SS_validering_v19.5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uisn-my.sharepoint.com/personal/266754_usn_no/Documents/USN/26V Bachelor/K-Spice/Validering/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uisn-my.sharepoint.com/personal/266754_usn_no/Documents/USN/26V Bachelor/K-Spice/GitHub/DynamicCO2Simulator/Documents and results/SS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1140" documentId="8_{CFF00B12-228D-441B-99FA-6C688BC7A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D0141F-7CF5-4FD2-B4E2-D765B1A5229D}"/>
+  <xr:revisionPtr revIDLastSave="1144" documentId="8_{CFF00B12-228D-441B-99FA-6C688BC7A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF007595-9D08-4385-8950-A38820AFEE6F}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="718" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="718" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Appendix A" sheetId="2" r:id="rId1"/>
@@ -976,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -989,432 +989,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="144">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF8F8F"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="84">
     <dxf>
       <fill>
         <patternFill>
@@ -2024,790 +1603,794 @@
 <file path=xl/volatileDependencies.xml><?xml version="1.0" encoding="utf-8"?>
 <volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <volType type="realTimeData">
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>9d5c4c7f-681c-4d0d-86f5-66cd5b8ea7ee</stp>
-        <tr r="E49" s="3"/>
-        <tr r="E49" s="10"/>
-        <tr r="E49" s="9"/>
-        <tr r="E49" s="4"/>
-        <tr r="E49" s="5"/>
-        <tr r="E49" s="8"/>
+        <stp>c8343858-b092-404f-8b90-61f5485b44ba</stp>
+        <tr r="E74" s="3"/>
+        <tr r="E74" s="10"/>
+        <tr r="E74" s="5"/>
+        <tr r="E74" s="9"/>
+        <tr r="E74" s="4"/>
+        <tr r="E74" s="8"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>bd2b4a86-1e68-443b-8660-145ec6ee539e</stp>
-        <tr r="E23" s="9"/>
-        <tr r="E23" s="3"/>
-        <tr r="E23" s="10"/>
-        <tr r="E23" s="5"/>
-        <tr r="E23" s="4"/>
-        <tr r="E23" s="8"/>
+        <stp>9a86445c-3411-4af9-956e-f8623d8515f0</stp>
+        <tr r="E46" s="4"/>
+        <tr r="E46" s="3"/>
+        <tr r="E46" s="5"/>
+        <tr r="E46" s="10"/>
+        <tr r="E46" s="9"/>
+        <tr r="E46" s="8"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>4a1f4aaf-6bb5-48b6-9216-9ee4cdf0daa0</stp>
+        <stp>c7bbb40d-f019-46d7-b6e2-63dd374873b0</stp>
+        <tr r="E62" s="8"/>
         <tr r="E62" s="4"/>
-        <tr r="E62" s="8"/>
+        <tr r="E62" s="10"/>
         <tr r="E62" s="3"/>
         <tr r="E62" s="9"/>
         <tr r="E62" s="5"/>
-        <tr r="E62" s="10"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>fbf50401-0aa5-4eba-a107-4a196e2fba11</stp>
-        <tr r="E66" s="3"/>
-        <tr r="E66" s="9"/>
-        <tr r="E66" s="8"/>
-        <tr r="E66" s="5"/>
-        <tr r="E66" s="10"/>
-        <tr r="E66" s="4"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>57455850-2af0-4613-9983-ab15c4f27263</stp>
-        <tr r="E83" s="9"/>
-        <tr r="E83" s="8"/>
-        <tr r="E83" s="10"/>
-        <tr r="E83" s="3"/>
-        <tr r="E83" s="4"/>
-        <tr r="E83" s="5"/>
+        <stp>83bbe0c2-966f-4a90-b43a-3819626df36e</stp>
+        <tr r="E94" s="10"/>
+        <tr r="E94" s="4"/>
+        <tr r="E94" s="8"/>
+        <tr r="E94" s="5"/>
+        <tr r="E94" s="9"/>
+        <tr r="E94" s="3"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>7a3b1101-75a4-4f66-857e-630e10e1577a</stp>
-        <tr r="E71" s="5"/>
-        <tr r="E71" s="10"/>
-        <tr r="E71" s="8"/>
-        <tr r="E71" s="3"/>
-        <tr r="E71" s="4"/>
-        <tr r="E71" s="9"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>75d1d1c2-1238-41fb-bec3-ace4baa72b2d</stp>
-        <tr r="E44" s="5"/>
-        <tr r="E44" s="4"/>
-        <tr r="E44" s="10"/>
-        <tr r="E44" s="8"/>
-        <tr r="E44" s="3"/>
-        <tr r="E44" s="9"/>
+        <stp>028bad3a-9b07-4792-b1e0-c8817f9dff26</stp>
+        <tr r="E15" s="3"/>
+        <tr r="E15" s="9"/>
+        <tr r="E15" s="10"/>
+        <tr r="E15" s="4"/>
+        <tr r="E15" s="5"/>
+        <tr r="E15" s="8"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>90d50af6-7575-44d9-87bc-6293685b2cd7</stp>
-        <tr r="E102" s="10"/>
-        <tr r="E102" s="9"/>
-        <tr r="E102" s="8"/>
-        <tr r="E102" s="5"/>
-        <tr r="E103" s="3"/>
-        <tr r="E103" s="4"/>
+        <stp>5920d337-8e55-4ada-a5e3-b12bca8eaf5f</stp>
+        <tr r="E18" s="9"/>
+        <tr r="E18" s="3"/>
+        <tr r="E18" s="4"/>
+        <tr r="E18" s="5"/>
+        <tr r="E18" s="10"/>
+        <tr r="E18" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>3f5e7736-1147-4f2f-b878-f1b23ada4c1e</stp>
+        <tr r="E27" s="5"/>
+        <tr r="E27" s="4"/>
+        <tr r="E27" s="3"/>
+        <tr r="E27" s="9"/>
+        <tr r="E27" s="10"/>
+        <tr r="E27" s="8"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>027784fe-a770-4bf3-ad01-566096c1714e</stp>
-        <tr r="E16" s="5"/>
-        <tr r="E16" s="4"/>
-        <tr r="E16" s="3"/>
-        <tr r="E16" s="10"/>
-        <tr r="E16" s="9"/>
-        <tr r="E16" s="8"/>
+        <stp>a1b82b47-ae96-4f5a-b54d-1e3ba138e184</stp>
+        <tr r="E95" s="9"/>
+        <tr r="E95" s="5"/>
+        <tr r="E96" s="3"/>
+        <tr r="E96" s="10"/>
+        <tr r="E95" s="4"/>
+        <tr r="E96" s="9"/>
+        <tr r="E96" s="8"/>
+        <tr r="E96" s="4"/>
+        <tr r="E95" s="3"/>
+        <tr r="E95" s="8"/>
+        <tr r="E95" s="10"/>
+        <tr r="E96" s="5"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>3e383428-aa36-46f2-af39-c59d1593cde2</stp>
-        <tr r="E17" s="5"/>
-        <tr r="E17" s="3"/>
-        <tr r="E17" s="10"/>
-        <tr r="E17" s="9"/>
-        <tr r="E17" s="4"/>
-        <tr r="E17" s="8"/>
+        <stp>79ea5e54-0686-4925-b189-39c3fb7de8e2</stp>
+        <tr r="E49" s="4"/>
+        <tr r="E49" s="3"/>
+        <tr r="E49" s="10"/>
+        <tr r="E49" s="5"/>
+        <tr r="E49" s="9"/>
+        <tr r="E49" s="8"/>
       </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>91ae8570-1691-483c-907c-27a460afe3aa</stp>
+        <stp>04d16aa8-44d9-44e6-b8ac-7364c30955c8</stp>
+        <tr r="E85" s="8"/>
+        <tr r="E85" s="9"/>
+        <tr r="E85" s="5"/>
+        <tr r="E85" s="10"/>
+        <tr r="E85" s="4"/>
+        <tr r="E85" s="3"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>ac6006c2-ce99-48a5-ab38-c4a2feaaab62</stp>
+        <tr r="E100" s="8"/>
+        <tr r="E100" s="9"/>
+        <tr r="E100" s="10"/>
+        <tr r="E101" s="4"/>
+        <tr r="E100" s="5"/>
+        <tr r="E101" s="3"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>cd4e25b8-6a99-42d0-b574-3c617949a9af</stp>
+        <tr r="E101" s="8"/>
+        <tr r="E101" s="9"/>
+        <tr r="E101" s="10"/>
+        <tr r="E102" s="4"/>
+        <tr r="E102" s="3"/>
+        <tr r="E101" s="5"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>8de30d66-4b29-4adb-adb6-423cf5d4905b</stp>
+        <tr r="E57" s="4"/>
+        <tr r="E57" s="3"/>
+        <tr r="E57" s="5"/>
+        <tr r="E57" s="8"/>
+        <tr r="E57" s="9"/>
+        <tr r="E57" s="10"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>56455e4c-135f-4601-b331-6ba37bb0cd7c</stp>
+        <tr r="E84" s="8"/>
+        <tr r="E84" s="3"/>
+        <tr r="E84" s="4"/>
+        <tr r="E84" s="10"/>
+        <tr r="E84" s="5"/>
+        <tr r="E84" s="9"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>387114d7-703e-4c99-8aaa-827800996e59</stp>
+        <tr r="E64" s="4"/>
+        <tr r="E64" s="5"/>
+        <tr r="E64" s="8"/>
+        <tr r="E64" s="3"/>
+        <tr r="E64" s="9"/>
+        <tr r="E64" s="10"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>0ce294f1-b134-4ed4-97cd-21aef2b05e69</stp>
+        <tr r="E26" s="10"/>
+        <tr r="E26" s="3"/>
+        <tr r="E26" s="9"/>
+        <tr r="E26" s="5"/>
+        <tr r="E26" s="4"/>
+        <tr r="E26" s="8"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>e2d7565e-bef3-4d55-a320-be67252225d8</stp>
+        <tr r="E63" s="8"/>
+        <tr r="E63" s="10"/>
+        <tr r="E63" s="4"/>
+        <tr r="E63" s="5"/>
+        <tr r="E63" s="9"/>
+        <tr r="E63" s="3"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>09641a41-8564-43cd-9f07-ea43ff7eb6e8</stp>
+        <tr r="E39" s="10"/>
+        <tr r="E39" s="3"/>
+        <tr r="E39" s="8"/>
+        <tr r="E39" s="5"/>
+        <tr r="E39" s="9"/>
+        <tr r="E39" s="4"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>dc12c136-0078-45a6-b4d2-1fc644c3fd87</stp>
+        <tr r="E42" s="9"/>
+        <tr r="E42" s="8"/>
+        <tr r="E42" s="4"/>
+        <tr r="E42" s="5"/>
+        <tr r="E42" s="10"/>
+        <tr r="E42" s="3"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>3d6273cc-69c8-46e4-a5f2-134a7182a6a8</stp>
+        <tr r="E104" s="8"/>
+        <tr r="E104" s="9"/>
+        <tr r="E105" s="3"/>
+        <tr r="E104" s="10"/>
+        <tr r="E105" s="4"/>
+        <tr r="E104" s="5"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>6bfb8daa-0c29-46da-b5d1-339a35e012cd</stp>
+        <tr r="E65" s="5"/>
+        <tr r="E65" s="10"/>
+        <tr r="E65" s="3"/>
+        <tr r="E65" s="9"/>
+        <tr r="E65" s="8"/>
+        <tr r="E65" s="4"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>64062d6f-3530-4491-83b0-bb75ec50d989</stp>
+        <tr r="E71" s="3"/>
+        <tr r="E71" s="8"/>
+        <tr r="E71" s="5"/>
+        <tr r="E71" s="9"/>
+        <tr r="E71" s="4"/>
+        <tr r="E71" s="10"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>937a363d-10b9-4cc9-b9ea-33487a771250</stp>
+        <tr r="E35" s="10"/>
+        <tr r="E35" s="3"/>
+        <tr r="E35" s="4"/>
+        <tr r="E35" s="5"/>
+        <tr r="E35" s="9"/>
+        <tr r="E35" s="8"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>595102c6-4e3b-4a87-99ea-75ddeabd3166</stp>
+        <tr r="E91" s="5"/>
+        <tr r="E91" s="3"/>
+        <tr r="E91" s="10"/>
+        <tr r="E91" s="8"/>
+        <tr r="E91" s="4"/>
+        <tr r="E91" s="9"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>b9c24e88-4bec-44a3-97d3-e6b8dcbc0be9</stp>
+        <tr r="E103" s="8"/>
+        <tr r="E103" s="9"/>
+        <tr r="E103" s="10"/>
+        <tr r="E104" s="4"/>
+        <tr r="E103" s="5"/>
+        <tr r="E104" s="3"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>11ec7add-f425-4037-9abc-a1af9983bbae</stp>
+        <tr r="E44" s="9"/>
+        <tr r="E44" s="5"/>
+        <tr r="E44" s="3"/>
+        <tr r="E44" s="8"/>
+        <tr r="E44" s="10"/>
+        <tr r="E44" s="4"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>031436f1-deb5-4ab7-b4b6-4858fccf7d0e</stp>
+        <tr r="E43" s="10"/>
+        <tr r="E43" s="3"/>
+        <tr r="E43" s="9"/>
+        <tr r="E43" s="8"/>
+        <tr r="E43" s="5"/>
+        <tr r="E43" s="4"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>df960432-c10f-4d89-af37-a6b672de44ca</stp>
+        <tr r="E73" s="10"/>
+        <tr r="E73" s="8"/>
+        <tr r="E73" s="5"/>
+        <tr r="E73" s="9"/>
+        <tr r="E73" s="3"/>
+        <tr r="E73" s="4"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>1fbc8935-7c47-4af0-8f33-6aa9c4fe02d1</stp>
+        <tr r="E34" s="9"/>
+        <tr r="E34" s="10"/>
+        <tr r="E34" s="4"/>
+        <tr r="E34" s="3"/>
+        <tr r="E34" s="5"/>
+        <tr r="E34" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>ac7289a4-1af0-49a7-ac18-5eca85fbf1f4</stp>
+        <tr r="E28" s="5"/>
+        <tr r="E40" s="9"/>
+        <tr r="E28" s="3"/>
+        <tr r="E28" s="4"/>
+        <tr r="E40" s="3"/>
+        <tr r="E40" s="4"/>
+        <tr r="E28" s="10"/>
+        <tr r="E40" s="10"/>
+        <tr r="E28" s="9"/>
+        <tr r="E40" s="5"/>
+        <tr r="E40" s="8"/>
+        <tr r="E28" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>990ce0f2-1daf-4671-a803-37ee2bfcca42</stp>
+        <tr r="E48" s="4"/>
+        <tr r="E48" s="9"/>
+        <tr r="E48" s="8"/>
+        <tr r="E48" s="3"/>
+        <tr r="E48" s="5"/>
+        <tr r="E48" s="10"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>627c2afd-1d1b-4c58-8309-e34afabdd599</stp>
+        <tr r="E98" s="3"/>
+        <tr r="E98" s="5"/>
+        <tr r="E97" s="10"/>
+        <tr r="E98" s="4"/>
+        <tr r="E97" s="4"/>
+        <tr r="E98" s="10"/>
+        <tr r="E98" s="8"/>
+        <tr r="E97" s="3"/>
+        <tr r="E97" s="9"/>
+        <tr r="E97" s="5"/>
+        <tr r="E97" s="8"/>
+        <tr r="E98" s="9"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>9d932b1a-4467-4d5a-91ba-04efc900c249</stp>
+        <tr r="E21" s="10"/>
+        <tr r="E21" s="9"/>
+        <tr r="E21" s="3"/>
+        <tr r="E21" s="4"/>
+        <tr r="E21" s="5"/>
+        <tr r="E21" s="8"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>d81303a6-bc77-4f79-bb27-960dac0679c5</stp>
+        <tr r="E45" s="8"/>
+        <tr r="E45" s="9"/>
+        <tr r="E45" s="10"/>
+        <tr r="E45" s="3"/>
+        <tr r="E45" s="4"/>
+        <tr r="E45" s="5"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>744b4ae5-6d7f-4383-b087-822b61723d93</stp>
+        <tr r="E14" s="4"/>
+        <tr r="E14" s="5"/>
+        <tr r="E14" s="10"/>
+        <tr r="E14" s="3"/>
+        <tr r="E14" s="9"/>
+        <tr r="E14" s="8"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>438bfaf5-5a41-4571-9f3f-3f8800d72c6f</stp>
+        <tr r="E38" s="3"/>
         <tr r="E38" s="5"/>
-        <tr r="E38" s="3"/>
         <tr r="E38" s="4"/>
         <tr r="E38" s="10"/>
         <tr r="E38" s="9"/>
         <tr r="E38" s="8"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>6481bef0-2c8e-4392-a6f3-42bb21311bd6</stp>
-        <tr r="E34" s="3"/>
-        <tr r="E34" s="10"/>
-        <tr r="E34" s="4"/>
-        <tr r="E34" s="5"/>
-        <tr r="E34" s="9"/>
-        <tr r="E34" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>d15a3e06-0e57-4e77-ae39-0475456f4777</stp>
-        <tr r="E104" s="10"/>
-        <tr r="E104" s="9"/>
-        <tr r="E104" s="8"/>
-        <tr r="E104" s="5"/>
-        <tr r="E105" s="3"/>
-        <tr r="E105" s="4"/>
+        <stp>70f10416-5b25-43dc-9dd6-cf367f3e9f61</stp>
+        <tr r="E52" s="3"/>
+        <tr r="E52" s="5"/>
+        <tr r="E52" s="10"/>
+        <tr r="E52" s="8"/>
+        <tr r="E52" s="9"/>
+        <tr r="E52" s="4"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>19723f82-608d-4b70-a198-20e957f42092</stp>
-        <tr r="E39" s="5"/>
-        <tr r="E39" s="4"/>
-        <tr r="E39" s="9"/>
-        <tr r="E39" s="10"/>
-        <tr r="E39" s="8"/>
-        <tr r="E39" s="3"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>0715cee8-d4c0-42c1-8f60-838facb9460a</stp>
-        <tr r="E88" s="10"/>
-        <tr r="E88" s="9"/>
-        <tr r="E88" s="5"/>
-        <tr r="E88" s="8"/>
-        <tr r="E88" s="3"/>
-        <tr r="E88" s="4"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>187cd913-4d72-43a4-8d07-985334e3deb2</stp>
-        <tr r="E73" s="5"/>
-        <tr r="E73" s="3"/>
-        <tr r="E73" s="4"/>
-        <tr r="E73" s="8"/>
-        <tr r="E73" s="10"/>
-        <tr r="E73" s="9"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>5592bd3d-4fc4-4133-a631-d59cc1f11825</stp>
-        <tr r="E48" s="9"/>
-        <tr r="E48" s="4"/>
-        <tr r="E48" s="3"/>
-        <tr r="E48" s="5"/>
-        <tr r="E48" s="8"/>
-        <tr r="E48" s="10"/>
+        <stp>cd1c8cb1-e4b8-45e1-a287-99042f336d16</stp>
+        <tr r="E102" s="9"/>
+        <tr r="E102" s="10"/>
+        <tr r="E103" s="3"/>
+        <tr r="E102" s="5"/>
+        <tr r="E103" s="4"/>
+        <tr r="E102" s="8"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>a807079f-c178-4de1-bd78-d42852f33521</stp>
-        <tr r="E21" s="4"/>
-        <tr r="E21" s="9"/>
-        <tr r="E21" s="5"/>
-        <tr r="E21" s="10"/>
-        <tr r="E21" s="3"/>
-        <tr r="E21" s="8"/>
+        <stp>f880ab96-ee74-43fb-ab8f-00a7ddb61aaa</stp>
+        <tr r="E47" s="9"/>
+        <tr r="E47" s="5"/>
+        <tr r="E47" s="10"/>
+        <tr r="E47" s="3"/>
+        <tr r="E47" s="8"/>
+        <tr r="E47" s="4"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>be378d92-f04d-48d4-90c0-ddc959575410</stp>
-        <tr r="E75" s="8"/>
-        <tr r="E75" s="4"/>
-        <tr r="E75" s="5"/>
-        <tr r="E75" s="3"/>
-        <tr r="E75" s="9"/>
-        <tr r="E75" s="10"/>
+        <stp>3ca9c5c7-e7e0-48df-82e5-67df802c4f14</stp>
+        <tr r="E41" s="5"/>
+        <tr r="E41" s="10"/>
+        <tr r="E41" s="9"/>
+        <tr r="E41" s="4"/>
+        <tr r="E41" s="8"/>
+        <tr r="E41" s="3"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>01303113-713c-4959-bc22-b9d4ccb48452</stp>
+        <tr r="E30" s="4"/>
+        <tr r="E30" s="3"/>
+        <tr r="E30" s="10"/>
+        <tr r="E30" s="5"/>
+        <tr r="E30" s="9"/>
+        <tr r="E30" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>7e9abcab-fa65-4134-a8e4-75684c883304</stp>
+        <tr r="E36" s="5"/>
+        <tr r="E36" s="3"/>
+        <tr r="E36" s="9"/>
+        <tr r="E36" s="10"/>
+        <tr r="E36" s="4"/>
+        <tr r="E36" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>95c4b29d-2be7-4736-a1f6-07afb2c6c489</stp>
+        <tr r="E22" s="10"/>
+        <tr r="E22" s="4"/>
+        <tr r="E22" s="9"/>
+        <tr r="E22" s="5"/>
+        <tr r="E22" s="3"/>
+        <tr r="E22" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>4519d9cc-dcad-4a38-a8a8-4fde5e940f3a</stp>
+        <tr r="E66" s="3"/>
+        <tr r="E66" s="5"/>
+        <tr r="E66" s="10"/>
+        <tr r="E66" s="4"/>
+        <tr r="E66" s="9"/>
+        <tr r="E66" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>9f97cab8-a75c-4613-83f9-01519b8d8503</stp>
+        <tr r="E68" s="5"/>
+        <tr r="E68" s="3"/>
+        <tr r="E68" s="8"/>
+        <tr r="E68" s="10"/>
+        <tr r="E68" s="9"/>
+        <tr r="E68" s="4"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>a921dd38-cfac-4dd8-a79b-2f92cf2cafd1</stp>
-        <tr r="E103" s="10"/>
-        <tr r="E103" s="9"/>
-        <tr r="E103" s="8"/>
-        <tr r="E103" s="5"/>
-        <tr r="E104" s="3"/>
-        <tr r="E104" s="4"/>
+        <stp>64421a47-b310-46c3-93a9-135a241fb46e</stp>
+        <tr r="E23" s="4"/>
+        <tr r="E23" s="10"/>
+        <tr r="E23" s="9"/>
+        <tr r="E23" s="3"/>
+        <tr r="E23" s="5"/>
+        <tr r="E23" s="8"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>31f7db58-1a75-413b-8f85-8c4045738267</stp>
-        <tr r="E41" s="9"/>
-        <tr r="E41" s="4"/>
-        <tr r="E41" s="8"/>
-        <tr r="E41" s="3"/>
-        <tr r="E41" s="10"/>
-        <tr r="E41" s="5"/>
+        <stp>ffec9319-a9a7-4872-9a52-4e30d621d623</stp>
+        <tr r="E80" s="10"/>
+        <tr r="E80" s="3"/>
+        <tr r="E80" s="4"/>
+        <tr r="E80" s="9"/>
+        <tr r="E80" s="8"/>
+        <tr r="E80" s="5"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>a6e9c856-071a-4053-8096-1bc4b52fc496</stp>
+        <tr r="E20" s="10"/>
+        <tr r="E20" s="9"/>
+        <tr r="E20" s="3"/>
+        <tr r="E20" s="5"/>
+        <tr r="E20" s="4"/>
+        <tr r="E20" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>f5828230-b21b-4cb1-8854-ff0b4fb4c941</stp>
+        <tr r="E75" s="4"/>
+        <tr r="E75" s="10"/>
+        <tr r="E75" s="5"/>
+        <tr r="E75" s="3"/>
+        <tr r="E75" s="8"/>
+        <tr r="E75" s="9"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>44a7477e-ad70-492c-a23d-1a709984a6ec</stp>
-        <tr r="E72" s="10"/>
-        <tr r="E72" s="8"/>
-        <tr r="E72" s="5"/>
-        <tr r="E72" s="3"/>
-        <tr r="E72" s="9"/>
-        <tr r="E72" s="4"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>3ca8c1fc-9011-4389-9edf-d01fdb92b813</stp>
-        <tr r="E79" s="4"/>
-        <tr r="E79" s="5"/>
-        <tr r="E79" s="10"/>
-        <tr r="E79" s="8"/>
-        <tr r="E79" s="3"/>
-        <tr r="E79" s="9"/>
+        <stp>feb2ddb7-cfed-4cd3-9de1-430de84fafac</stp>
+        <tr r="E83" s="3"/>
+        <tr r="E83" s="5"/>
+        <tr r="E83" s="4"/>
+        <tr r="E83" s="9"/>
+        <tr r="E83" s="8"/>
+        <tr r="E83" s="10"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>38619558-58f7-4f55-bd77-92d64ed1b1e2</stp>
-        <tr r="E76" s="9"/>
-        <tr r="E76" s="10"/>
-        <tr r="E76" s="4"/>
-        <tr r="E76" s="5"/>
-        <tr r="E76" s="3"/>
-        <tr r="E76" s="8"/>
+        <stp>c148ea09-a094-4792-a75a-88271572dbb7</stp>
+        <tr r="E72" s="10"/>
+        <tr r="E72" s="3"/>
+        <tr r="E72" s="5"/>
+        <tr r="E72" s="9"/>
+        <tr r="E72" s="4"/>
+        <tr r="E72" s="8"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>e4af7d6e-e902-47f0-8970-39ff306b6f3e</stp>
-        <tr r="E55" s="4"/>
-        <tr r="E55" s="8"/>
-        <tr r="E55" s="9"/>
-        <tr r="E55" s="5"/>
-        <tr r="E55" s="3"/>
-        <tr r="E55" s="10"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>dcf599bc-40ab-430d-a957-fbcf12cd1150</stp>
-        <tr r="E100" s="10"/>
-        <tr r="E100" s="9"/>
-        <tr r="E100" s="8"/>
-        <tr r="E100" s="5"/>
-        <tr r="E101" s="3"/>
-        <tr r="E101" s="4"/>
+        <stp>505c210a-aead-44ed-9104-d07dc82d2ee9</stp>
+        <tr r="E76" s="5"/>
+        <tr r="E76" s="10"/>
+        <tr r="E76" s="8"/>
+        <tr r="E76" s="9"/>
+        <tr r="E76" s="4"/>
+        <tr r="E76" s="3"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>0c40caef-e7a0-4493-8ab5-47d35fd9591b</stp>
-        <tr r="E30" s="5"/>
-        <tr r="E30" s="4"/>
-        <tr r="E30" s="9"/>
-        <tr r="E30" s="3"/>
-        <tr r="E30" s="10"/>
-        <tr r="E30" s="8"/>
+        <stp>08190924-6ee0-4c2e-b529-40ad012428ce</stp>
+        <tr r="E88" s="4"/>
+        <tr r="E88" s="8"/>
+        <tr r="E88" s="9"/>
+        <tr r="E88" s="10"/>
+        <tr r="E88" s="5"/>
+        <tr r="E88" s="3"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>71830d57-19e0-4840-af73-5780df96d25b</stp>
-        <tr r="E58" s="10"/>
-        <tr r="E58" s="3"/>
-        <tr r="E58" s="5"/>
-        <tr r="E58" s="8"/>
-        <tr r="E58" s="9"/>
-        <tr r="E58" s="4"/>
+        <stp>b500fbb7-3068-4947-8f49-393ba6e3c252</stp>
+        <tr r="E19" s="9"/>
+        <tr r="E19" s="10"/>
+        <tr r="E19" s="3"/>
+        <tr r="E19" s="4"/>
+        <tr r="E19" s="5"/>
+        <tr r="E19" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>ac18c021-8a0d-4ba8-aa03-809a707d5978</stp>
+        <tr r="E29" s="9"/>
+        <tr r="E29" s="10"/>
+        <tr r="E29" s="5"/>
+        <tr r="E29" s="3"/>
+        <tr r="E29" s="4"/>
+        <tr r="E29" s="8"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>6365b204-6c4b-41d0-85f5-1e4bb9d06a9b</stp>
+        <tr r="E55" s="10"/>
+        <tr r="E55" s="4"/>
+        <tr r="E55" s="9"/>
+        <tr r="E55" s="3"/>
+        <tr r="E55" s="8"/>
+        <tr r="E55" s="5"/>
+      </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>0425aa43-e881-49a1-b443-94065d7a19cf</stp>
+        <tr r="E61" s="9"/>
+        <tr r="E61" s="8"/>
+        <tr r="E61" s="4"/>
+        <tr r="E61" s="10"/>
+        <tr r="E61" s="3"/>
+        <tr r="E61" s="5"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>a2ff433b-9b67-4088-82fd-34ae510d1b71</stp>
-        <tr r="E74" s="3"/>
-        <tr r="E74" s="5"/>
-        <tr r="E74" s="4"/>
-        <tr r="E74" s="10"/>
-        <tr r="E74" s="9"/>
-        <tr r="E74" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>f90025f6-3668-4cdb-850b-f49cf884ec48</stp>
-        <tr r="E61" s="5"/>
-        <tr r="E61" s="3"/>
-        <tr r="E61" s="9"/>
-        <tr r="E61" s="10"/>
-        <tr r="E61" s="8"/>
-        <tr r="E61" s="4"/>
+        <stp>30b236d4-6739-4699-9b8d-6c8eb713e94f</stp>
+        <tr r="E17" s="3"/>
+        <tr r="E17" s="5"/>
+        <tr r="E17" s="10"/>
+        <tr r="E17" s="9"/>
+        <tr r="E17" s="4"/>
+        <tr r="E17" s="8"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>e343e209-b945-40cd-bfa5-7e6927587651</stp>
-        <tr r="E35" s="9"/>
-        <tr r="E35" s="4"/>
-        <tr r="E35" s="5"/>
-        <tr r="E35" s="10"/>
-        <tr r="E35" s="3"/>
-        <tr r="E35" s="8"/>
+        <stp>9e05f792-f0bf-4359-8ac6-1d0ccce8b55a</stp>
+        <tr r="E13" s="4"/>
+        <tr r="E13" s="10"/>
+        <tr r="E13" s="3"/>
+        <tr r="E13" s="5"/>
+        <tr r="E13" s="9"/>
+        <tr r="E13" s="8"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>64513572-46fb-4ecd-8476-e51d4ad94037</stp>
-        <tr r="E15" s="9"/>
-        <tr r="E15" s="10"/>
-        <tr r="E15" s="4"/>
-        <tr r="E15" s="5"/>
-        <tr r="E15" s="3"/>
-        <tr r="E15" s="8"/>
+        <stp>a77c7921-b50f-48d4-a8b4-d2ac1aa59456</stp>
+        <tr r="E79" s="3"/>
+        <tr r="E79" s="4"/>
+        <tr r="E79" s="8"/>
+        <tr r="E79" s="9"/>
+        <tr r="E79" s="5"/>
+        <tr r="E79" s="10"/>
       </tp>
       <tp>
         <v>1</v>
         <stp/>
-        <stp>606a1020-d8fe-4c46-a2e2-cd4825ea7d15</stp>
-        <tr r="E28" s="4"/>
-        <tr r="E28" s="10"/>
-        <tr r="E40" s="5"/>
-        <tr r="E40" s="9"/>
-        <tr r="E28" s="3"/>
-        <tr r="E40" s="8"/>
-        <tr r="E40" s="10"/>
-        <tr r="E40" s="4"/>
-        <tr r="E28" s="5"/>
-        <tr r="E28" s="9"/>
-        <tr r="E40" s="3"/>
-        <tr r="E28" s="8"/>
+        <stp>a8e87951-ebcc-4b2a-bc2a-39927a34e213</stp>
+        <tr r="E67" s="4"/>
+        <tr r="E67" s="5"/>
+        <tr r="E67" s="9"/>
+        <tr r="E67" s="3"/>
+        <tr r="E67" s="8"/>
+        <tr r="E67" s="10"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>427977b9-4659-484d-bcae-411d4dfbcbed</stp>
-        <tr r="E84" s="5"/>
-        <tr r="E84" s="9"/>
-        <tr r="E84" s="10"/>
-        <tr r="E84" s="3"/>
-        <tr r="E84" s="8"/>
-        <tr r="E84" s="4"/>
+        <stp>f6c2e34a-cb95-40ca-8ad5-8ab658bbed36</stp>
+        <tr r="E31" s="10"/>
+        <tr r="E31" s="9"/>
+        <tr r="E31" s="3"/>
+        <tr r="E31" s="4"/>
+        <tr r="E31" s="5"/>
+        <tr r="E31" s="8"/>
       </tp>
+    </main>
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>8a1e3cd9-b4d8-4c67-87e9-50afc61b4738</stp>
-        <tr r="E46" s="9"/>
-        <tr r="E46" s="10"/>
-        <tr r="E46" s="3"/>
-        <tr r="E46" s="8"/>
-        <tr r="E46" s="4"/>
-        <tr r="E46" s="5"/>
+        <stp>ee630cca-d920-497e-9e48-086e8420ea53</stp>
+        <tr r="E58" s="9"/>
+        <tr r="E58" s="3"/>
+        <tr r="E58" s="5"/>
+        <tr r="E58" s="8"/>
+        <tr r="E58" s="4"/>
+        <tr r="E58" s="10"/>
       </tp>
     </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
+    <main first="rtdsrv.166a02754216417ea584dd8fc2df95dd">
       <tp>
         <v>1</v>
         <stp/>
-        <stp>2503282a-801f-4d70-8146-b0746756921d</stp>
-        <tr r="E26" s="4"/>
-        <tr r="E26" s="10"/>
-        <tr r="E26" s="9"/>
-        <tr r="E26" s="5"/>
-        <tr r="E26" s="3"/>
-        <tr r="E26" s="8"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>0898d4b1-91b7-4510-9d08-7ffd9d74d366</stp>
-        <tr r="E31" s="4"/>
-        <tr r="E31" s="10"/>
-        <tr r="E31" s="5"/>
-        <tr r="E31" s="9"/>
-        <tr r="E31" s="3"/>
-        <tr r="E31" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>105227a4-73e5-48d7-9915-9c47ebe6e3d5</stp>
-        <tr r="E42" s="5"/>
-        <tr r="E42" s="10"/>
-        <tr r="E42" s="9"/>
-        <tr r="E42" s="3"/>
-        <tr r="E42" s="8"/>
-        <tr r="E42" s="4"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>cc091ec7-11d1-44ed-91d9-a3255c10bc06</stp>
-        <tr r="E101" s="10"/>
-        <tr r="E101" s="9"/>
-        <tr r="E101" s="8"/>
-        <tr r="E101" s="5"/>
-        <tr r="E102" s="3"/>
-        <tr r="E102" s="4"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>dd8d0ddc-f6b1-4743-89ef-d2f0c089a759</stp>
-        <tr r="E97" s="9"/>
-        <tr r="E98" s="4"/>
-        <tr r="E97" s="3"/>
-        <tr r="E97" s="5"/>
-        <tr r="E98" s="10"/>
-        <tr r="E98" s="8"/>
-        <tr r="E97" s="10"/>
-        <tr r="E98" s="3"/>
-        <tr r="E97" s="4"/>
-        <tr r="E98" s="9"/>
-        <tr r="E97" s="8"/>
-        <tr r="E98" s="5"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>c5167290-18ec-414c-8bd7-4e64cedaf42e</stp>
-        <tr r="E91" s="4"/>
-        <tr r="E91" s="10"/>
-        <tr r="E91" s="8"/>
-        <tr r="E91" s="3"/>
-        <tr r="E91" s="9"/>
-        <tr r="E91" s="5"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>2cfca661-41cc-4410-b3ec-abca8c335013</stp>
-        <tr r="E43" s="4"/>
-        <tr r="E43" s="9"/>
-        <tr r="E43" s="10"/>
-        <tr r="E43" s="5"/>
-        <tr r="E43" s="8"/>
-        <tr r="E43" s="3"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>0c243d4e-0e99-4204-866d-00b0060b069c</stp>
-        <tr r="E45" s="4"/>
-        <tr r="E45" s="5"/>
-        <tr r="E45" s="9"/>
-        <tr r="E45" s="10"/>
-        <tr r="E45" s="3"/>
-        <tr r="E45" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>c4aaceef-8df9-4a93-8e9a-df55ef9d3e5b</stp>
-        <tr r="E68" s="9"/>
-        <tr r="E68" s="3"/>
-        <tr r="E68" s="4"/>
-        <tr r="E68" s="10"/>
-        <tr r="E68" s="5"/>
-        <tr r="E68" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>5e991a53-fd02-40e6-b1a7-efb6ed02e1c4</stp>
-        <tr r="E96" s="4"/>
-        <tr r="E95" s="10"/>
-        <tr r="E96" s="10"/>
-        <tr r="E95" s="3"/>
-        <tr r="E95" s="8"/>
-        <tr r="E96" s="9"/>
-        <tr r="E95" s="4"/>
-        <tr r="E95" s="9"/>
-        <tr r="E96" s="5"/>
-        <tr r="E96" s="8"/>
-        <tr r="E95" s="5"/>
-        <tr r="E96" s="3"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>a7770fa0-ebe8-4bce-879a-f4b678841bb8</stp>
-        <tr r="E29" s="4"/>
-        <tr r="E29" s="10"/>
-        <tr r="E29" s="9"/>
-        <tr r="E29" s="3"/>
-        <tr r="E29" s="5"/>
-        <tr r="E29" s="8"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>bc74ff53-95ee-4b88-9040-710ec222d41b</stp>
-        <tr r="E27" s="5"/>
-        <tr r="E27" s="9"/>
-        <tr r="E27" s="3"/>
-        <tr r="E27" s="4"/>
-        <tr r="E27" s="10"/>
-        <tr r="E27" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>e51473d4-cda3-41f0-bd11-517bcdea3648</stp>
-        <tr r="E94" s="5"/>
-        <tr r="E94" s="3"/>
-        <tr r="E94" s="10"/>
-        <tr r="E94" s="9"/>
-        <tr r="E94" s="4"/>
-        <tr r="E94" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>7688c22e-bfce-483f-8cc4-09fdc92c0dc5</stp>
-        <tr r="E52" s="4"/>
-        <tr r="E52" s="3"/>
-        <tr r="E52" s="5"/>
-        <tr r="E52" s="8"/>
-        <tr r="E52" s="10"/>
-        <tr r="E52" s="9"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>adc1795d-27c3-42cd-96c5-a251066addde</stp>
-        <tr r="E57" s="4"/>
-        <tr r="E57" s="5"/>
-        <tr r="E57" s="3"/>
-        <tr r="E57" s="9"/>
-        <tr r="E57" s="10"/>
-        <tr r="E57" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>419ecf23-52eb-466a-95a2-4a2d3246391d</stp>
-        <tr r="E67" s="4"/>
-        <tr r="E67" s="5"/>
-        <tr r="E67" s="9"/>
-        <tr r="E67" s="8"/>
-        <tr r="E67" s="3"/>
-        <tr r="E67" s="10"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>7b98104e-5811-48de-95c6-89c89e2294b0</stp>
-        <tr r="E65" s="4"/>
-        <tr r="E65" s="8"/>
-        <tr r="E65" s="5"/>
-        <tr r="E65" s="3"/>
-        <tr r="E65" s="10"/>
-        <tr r="E65" s="9"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>72e2e5e5-a777-4181-9d8e-939f2ca8e584</stp>
-        <tr r="E13" s="10"/>
-        <tr r="E13" s="9"/>
-        <tr r="E13" s="3"/>
-        <tr r="E13" s="4"/>
-        <tr r="E13" s="5"/>
-        <tr r="E13" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>850b9e9e-5f11-492d-9c8e-54d57a3d9f39</stp>
-        <tr r="E85" s="5"/>
-        <tr r="E85" s="8"/>
-        <tr r="E85" s="3"/>
-        <tr r="E85" s="10"/>
-        <tr r="E85" s="9"/>
-        <tr r="E85" s="4"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>81dd65c8-0bf4-493b-86ff-80e3089a9382</stp>
-        <tr r="E14" s="3"/>
-        <tr r="E14" s="10"/>
-        <tr r="E14" s="5"/>
-        <tr r="E14" s="4"/>
-        <tr r="E14" s="9"/>
-        <tr r="E14" s="8"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>a233f6ed-2ad9-49be-a53f-acb237ed08f2</stp>
-        <tr r="E36" s="5"/>
-        <tr r="E36" s="4"/>
-        <tr r="E36" s="9"/>
-        <tr r="E36" s="10"/>
-        <tr r="E36" s="3"/>
-        <tr r="E36" s="8"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>2cf051bd-1e9e-4231-abe0-8998ec6e2a2f</stp>
-        <tr r="E19" s="10"/>
-        <tr r="E19" s="4"/>
-        <tr r="E19" s="3"/>
-        <tr r="E19" s="9"/>
-        <tr r="E19" s="5"/>
-        <tr r="E19" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>07fb628f-8a60-419c-adce-072e8bf8af83</stp>
-        <tr r="E80" s="5"/>
-        <tr r="E80" s="10"/>
-        <tr r="E80" s="8"/>
-        <tr r="E80" s="3"/>
-        <tr r="E80" s="4"/>
-        <tr r="E80" s="9"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>ce60390f-6e46-4033-857f-4a5ffd26ae7a</stp>
-        <tr r="E20" s="4"/>
-        <tr r="E20" s="9"/>
-        <tr r="E20" s="3"/>
-        <tr r="E20" s="10"/>
-        <tr r="E20" s="5"/>
-        <tr r="E20" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>3ad1fe5c-02d8-4036-a8a9-0b53286e6792</stp>
-        <tr r="E18" s="5"/>
-        <tr r="E18" s="9"/>
-        <tr r="E18" s="3"/>
-        <tr r="E18" s="4"/>
-        <tr r="E18" s="10"/>
-        <tr r="E18" s="8"/>
-      </tp>
-    </main>
-    <main first="rtdsrv.9009390795e3422f9082ccfc06846f89">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>8fa9b1f8-4407-49f9-b3d6-f3b48c0eeaa1</stp>
-        <tr r="E63" s="9"/>
-        <tr r="E63" s="4"/>
-        <tr r="E63" s="8"/>
-        <tr r="E63" s="10"/>
-        <tr r="E63" s="5"/>
-        <tr r="E63" s="3"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>c95c5f74-e0dc-41a2-8c93-697d4f16fa22</stp>
-        <tr r="E22" s="4"/>
-        <tr r="E22" s="10"/>
-        <tr r="E22" s="3"/>
-        <tr r="E22" s="5"/>
-        <tr r="E22" s="9"/>
-        <tr r="E22" s="8"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>6f8434f9-76d6-42c5-afbe-c0ec35e04813</stp>
-        <tr r="E64" s="8"/>
-        <tr r="E64" s="3"/>
-        <tr r="E64" s="10"/>
-        <tr r="E64" s="5"/>
-        <tr r="E64" s="9"/>
-        <tr r="E64" s="4"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>0b7058cb-f8c5-4a42-974b-569d41cd1245</stp>
-        <tr r="E47" s="3"/>
-        <tr r="E47" s="4"/>
-        <tr r="E47" s="9"/>
-        <tr r="E47" s="5"/>
-        <tr r="E47" s="10"/>
-        <tr r="E47" s="8"/>
+        <stp>6d17bc99-b5c7-44da-a5c4-164fe7e47969</stp>
+        <tr r="E16" s="9"/>
+        <tr r="E16" s="10"/>
+        <tr r="E16" s="4"/>
+        <tr r="E16" s="3"/>
+        <tr r="E16" s="5"/>
+        <tr r="E16" s="8"/>
       </tp>
     </main>
   </volType>
@@ -27550,16 +27133,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>317358</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123539</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2984358</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>36948</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>544516</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>94913</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>146198</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>8322</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -27588,16 +27171,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2996044</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>51954</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>227157</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>157883</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>153214</xdr:rowOff>
+      <xdr:rowOff>7048</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28461,7 +28044,7 @@
       <c r="S1" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="11" t="s">
         <v>267</v>
       </c>
     </row>
@@ -32381,48 +31964,26 @@
       <c r="A138" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="47" priority="10">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="11">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="12">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
-    <cfRule type="expression" dxfId="44" priority="7">
-      <formula>ABS(G99)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="8">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="9">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H101:H104">
-    <cfRule type="expression" dxfId="41" priority="4">
+    <cfRule type="expression" dxfId="20" priority="4">
       <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="5">
+    <cfRule type="expression" dxfId="19" priority="5">
       <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="6">
+    <cfRule type="expression" dxfId="18" priority="6">
       <formula>ABS(H101)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G100:G104">
-    <cfRule type="expression" dxfId="38" priority="1">
-      <formula>ABS(G100)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="2">
-      <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="3">
-      <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34456,48 +34017,26 @@
       <c r="A144" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="35" priority="10">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="11">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="12">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
-    <cfRule type="expression" dxfId="32" priority="7">
-      <formula>ABS(G99)&gt;10</formula>
+  <conditionalFormatting sqref="H101:H104">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="8">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="9">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G103:G104 H101:H104">
-    <cfRule type="expression" dxfId="29" priority="4">
-      <formula>ABS(G101)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="5">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="6">
-      <formula>ABS(G101)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G100:G102">
-    <cfRule type="expression" dxfId="26" priority="1">
-      <formula>ABS(G100)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
-      <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
-      <formula>ABS(G100)&lt;5</formula>
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>ABS(H101)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36717,36 +36256,25 @@
       <c r="A138" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="23" priority="7">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="8">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="9">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99:G104">
-    <cfRule type="expression" dxfId="14" priority="4">
-      <formula>ABS(G99)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="5">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="6">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H101:H104">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>ABS(H101)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38781,26 +38309,15 @@
       <c r="A144" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="8" priority="7">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>ABS(G13)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G99:G104">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>ABS(G99)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
-      <formula>ABS(G99)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H101:H104">
@@ -38973,7 +38490,7 @@
         <v>31</v>
       </c>
       <c r="G13" t="e">
-        <f t="shared" ref="G13:G23" si="0">100*(E13-B13)/B13</f>
+        <f>100*(E13-B13)/B13</f>
         <v>#N/A</v>
       </c>
       <c r="H13" t="s">
@@ -39002,7 +38519,7 @@
         <v>33</v>
       </c>
       <c r="G14" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G13:G23" si="0">100*(E14-B14)/B14</f>
         <v>#N/A</v>
       </c>
       <c r="H14" t="s">
@@ -41033,36 +40550,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="143" priority="10">
+    <cfRule type="expression" dxfId="83" priority="10">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="11">
+    <cfRule type="expression" dxfId="82" priority="11">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="12">
+    <cfRule type="expression" dxfId="81" priority="12">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100 H102:H105">
-    <cfRule type="expression" dxfId="137" priority="4">
+  <conditionalFormatting sqref="G100:G105">
+    <cfRule type="expression" dxfId="80" priority="1">
       <formula>ABS(G100)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="5">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="135" priority="6">
+    <cfRule type="expression" dxfId="78" priority="3">
       <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G101:G105">
-    <cfRule type="expression" dxfId="134" priority="1">
-      <formula>ABS(G101)&gt;10</formula>
+  <conditionalFormatting sqref="H102:H105">
+    <cfRule type="expression" dxfId="77" priority="4">
+      <formula>ABS(H102)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="2">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
+    <cfRule type="expression" dxfId="76" priority="5">
+      <formula>AND(ABS(H102)&gt;=5,ABS(H102)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="3">
-      <formula>ABS(G101)&lt;5</formula>
+    <cfRule type="expression" dxfId="75" priority="6">
+      <formula>ABS(H102)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -43106,36 +42623,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G13:G98 H71 H79">
-    <cfRule type="expression" dxfId="131" priority="7">
+    <cfRule type="expression" dxfId="74" priority="7">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="8">
+    <cfRule type="expression" dxfId="73" priority="8">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="9">
+    <cfRule type="expression" dxfId="72" priority="9">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100 H102:H105 G105">
-    <cfRule type="expression" dxfId="128" priority="4">
+  <conditionalFormatting sqref="G100:G105">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>ABS(G100)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="5">
+    <cfRule type="expression" dxfId="70" priority="2">
       <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="6">
+    <cfRule type="expression" dxfId="69" priority="3">
       <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G101:G104">
-    <cfRule type="expression" dxfId="125" priority="1">
-      <formula>ABS(G101)&gt;10</formula>
+  <conditionalFormatting sqref="H102:H105">
+    <cfRule type="expression" dxfId="68" priority="4">
+      <formula>ABS(H102)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="2">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
+    <cfRule type="expression" dxfId="67" priority="5">
+      <formula>AND(ABS(H102)&gt;=5,ABS(H102)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="3">
-      <formula>ABS(G101)&lt;5</formula>
+    <cfRule type="expression" dxfId="66" priority="6">
+      <formula>ABS(H102)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45355,47 +44872,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="122" priority="13">
+    <cfRule type="expression" dxfId="65" priority="13">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="14">
+    <cfRule type="expression" dxfId="64" priority="14">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="15">
+    <cfRule type="expression" dxfId="63" priority="15">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100">
-    <cfRule type="expression" dxfId="116" priority="7">
+  <conditionalFormatting sqref="G100:G105">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>ABS(G100)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="115" priority="8">
+    <cfRule type="expression" dxfId="61" priority="2">
       <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="9">
+    <cfRule type="expression" dxfId="60" priority="3">
       <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H102:H105">
-    <cfRule type="expression" dxfId="113" priority="4">
+    <cfRule type="expression" dxfId="59" priority="4">
       <formula>ABS(H102)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="5">
+    <cfRule type="expression" dxfId="58" priority="5">
       <formula>AND(ABS(H102)&gt;=5,ABS(H102)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="6">
+    <cfRule type="expression" dxfId="57" priority="6">
       <formula>ABS(H102)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G101:G105">
-    <cfRule type="expression" dxfId="110" priority="1">
-      <formula>ABS(G101)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="109" priority="2">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="108" priority="3">
-      <formula>ABS(G101)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47427,47 +46933,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="107" priority="10">
+    <cfRule type="expression" dxfId="56" priority="10">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="11">
+    <cfRule type="expression" dxfId="55" priority="11">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="12">
+    <cfRule type="expression" dxfId="54" priority="12">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100">
-    <cfRule type="expression" dxfId="104" priority="7">
+  <conditionalFormatting sqref="G100:G105">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>ABS(G100)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="8">
+    <cfRule type="expression" dxfId="52" priority="2">
       <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="9">
+    <cfRule type="expression" dxfId="51" priority="3">
       <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G104:G105 H102:H105">
-    <cfRule type="expression" dxfId="101" priority="4">
-      <formula>ABS(G102)&gt;10</formula>
+  <conditionalFormatting sqref="H102:H105">
+    <cfRule type="expression" dxfId="50" priority="4">
+      <formula>ABS(H102)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="5">
-      <formula>AND(ABS(G102)&gt;=5,ABS(G102)&lt;10)</formula>
+    <cfRule type="expression" dxfId="49" priority="5">
+      <formula>AND(ABS(H102)&gt;=5,ABS(H102)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="6">
-      <formula>ABS(G102)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G101:G103">
-    <cfRule type="expression" dxfId="98" priority="1">
-      <formula>ABS(G101)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="2">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="3">
-      <formula>ABS(G101)&lt;5</formula>
+    <cfRule type="expression" dxfId="48" priority="6">
+      <formula>ABS(H102)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -49687,48 +49182,26 @@
       <c r="A138" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="95" priority="10">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="11">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="12">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
-    <cfRule type="expression" dxfId="92" priority="7">
-      <formula>ABS(G99)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="8">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="9">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H101:H104">
-    <cfRule type="expression" dxfId="89" priority="4">
+    <cfRule type="expression" dxfId="44" priority="4">
       <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="5">
+    <cfRule type="expression" dxfId="43" priority="5">
       <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="6">
+    <cfRule type="expression" dxfId="42" priority="6">
       <formula>ABS(H101)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G100:G104">
-    <cfRule type="expression" dxfId="86" priority="1">
-      <formula>ABS(G100)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="2">
-      <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="3">
-      <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -51762,48 +51235,26 @@
       <c r="A144" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="83" priority="10">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="11">
+    <cfRule type="expression" dxfId="40" priority="2">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="12">
+    <cfRule type="expression" dxfId="39" priority="3">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
-    <cfRule type="expression" dxfId="80" priority="7">
-      <formula>ABS(G99)&gt;10</formula>
+  <conditionalFormatting sqref="H101:H104">
+    <cfRule type="expression" dxfId="38" priority="4">
+      <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="8">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
+    <cfRule type="expression" dxfId="37" priority="5">
+      <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="9">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G103:G104 H101:H104">
-    <cfRule type="expression" dxfId="77" priority="4">
-      <formula>ABS(G101)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="5">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="6">
-      <formula>ABS(G101)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G100:G102">
-    <cfRule type="expression" dxfId="74" priority="1">
-      <formula>ABS(G100)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="2">
-      <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="3">
-      <formula>ABS(G100)&lt;5</formula>
+    <cfRule type="expression" dxfId="36" priority="6">
+      <formula>ABS(H101)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -54023,48 +53474,26 @@
       <c r="A138" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="71" priority="10">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="11">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="12">
+    <cfRule type="expression" dxfId="33" priority="3">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
-    <cfRule type="expression" dxfId="68" priority="7">
-      <formula>ABS(G99)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="8">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="9">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H101:H104">
-    <cfRule type="expression" dxfId="65" priority="4">
+    <cfRule type="expression" dxfId="32" priority="4">
       <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="5">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="6">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>ABS(H101)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G100:G104">
-    <cfRule type="expression" dxfId="62" priority="1">
-      <formula>ABS(G100)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="2">
-      <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="3">
-      <formula>ABS(G100)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -56098,48 +55527,26 @@
       <c r="A144" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G13:G98">
-    <cfRule type="expression" dxfId="59" priority="10">
+  <conditionalFormatting sqref="G13:G104">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>ABS(G13)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="11">
+    <cfRule type="expression" dxfId="28" priority="2">
       <formula>AND(ABS(G13)&gt;=5,ABS(G13)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="12">
+    <cfRule type="expression" dxfId="27" priority="3">
       <formula>ABS(G13)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
-    <cfRule type="expression" dxfId="56" priority="7">
-      <formula>ABS(G99)&gt;10</formula>
+  <conditionalFormatting sqref="H101:H104">
+    <cfRule type="expression" dxfId="26" priority="4">
+      <formula>ABS(H101)&gt;10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="8">
-      <formula>AND(ABS(G99)&gt;=5,ABS(G99)&lt;10)</formula>
+    <cfRule type="expression" dxfId="25" priority="5">
+      <formula>AND(ABS(H101)&gt;=5,ABS(H101)&lt;10)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="9">
-      <formula>ABS(G99)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G103:G104 H101:H104">
-    <cfRule type="expression" dxfId="53" priority="4">
-      <formula>ABS(G101)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="5">
-      <formula>AND(ABS(G101)&gt;=5,ABS(G101)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="6">
-      <formula>ABS(G101)&lt;5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G100:G102">
-    <cfRule type="expression" dxfId="50" priority="1">
-      <formula>ABS(G100)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="2">
-      <formula>AND(ABS(G100)&gt;=5,ABS(G100)&lt;10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="3">
-      <formula>ABS(G100)&lt;5</formula>
+    <cfRule type="expression" dxfId="24" priority="6">
+      <formula>ABS(H101)&lt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -56289,18 +55696,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -56322,6 +55729,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14C74204-B257-4774-95D3-48DA2FC77ABC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B548BEB2-461E-4C8E-9111-F3B7B3EEF147}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -56337,14 +55752,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14C74204-B257-4774-95D3-48DA2FC77ABC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{3b8294be-1daf-4d3e-a6ad-d65452cc3d53}" enabled="1" method="Standard" siteId="{bf7cb870-b378-42ab-a618-31704bc2e9b7}" removed="0"/>
